--- a/Design/Requirements/Use_case_Description/Use_case_Description.xlsx
+++ b/Design/Requirements/Use_case_Description/Use_case_Description.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oscar/Desktop/Upbit_Trade_V2/Design/Requirements/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oscar/Desktop/Binance_Auto/Design/Requirements/Use_case_Description/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CEEFBD8-E0A5-5743-96C4-BC853CDBDC6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F237155A-53D0-F741-A8CF-61AC0B063473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23040" yWindow="600" windowWidth="23040" windowHeight="23340" xr2:uid="{504CCFC5-5E96-984B-88EF-26DFAFC547FE}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="46080" windowHeight="25920" xr2:uid="{504CCFC5-5E96-984B-88EF-26DFAFC547FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1069,7 +1069,9 @@
       <c r="B19" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="11"/>
+      <c r="C19" s="11">
+        <v>616518</v>
+      </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="6"/>
